--- a/docs/integrations/exceltogo/sample-import-template.xlsx
+++ b/docs/integrations/exceltogo/sample-import-template.xlsx
@@ -5095,7 +5095,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
-      <formula1>DATE(2020,1,1)</formula1>
+      <formula1>43831</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
